--- a/libertadores/datasets_liberta/resultados_fase_3.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_3.xlsx
@@ -7,8 +7,8 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Rodada 32" sheetId="1" r:id="rId1"/>
-    <sheet name="Rodada 33" sheetId="2" r:id="rId2"/>
+    <sheet name="Rodada 13" sheetId="1" r:id="rId1"/>
+    <sheet name="Rodada 14" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -454,19 +454,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>108.52</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>105.72</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -474,19 +474,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>92.62</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>94.47</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -494,19 +494,19 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>136.52</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>111.22</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -514,19 +514,19 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>87.92</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>97.62</v>
       </c>
     </row>
   </sheetData>
@@ -564,19 +564,13 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
       <c r="E2" t="s">
         <v>10</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -584,19 +578,13 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
       <c r="E3" t="s">
         <v>11</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -604,19 +592,13 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
       <c r="E4" t="s">
         <v>12</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -624,19 +606,13 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
       <c r="E5" t="s">
         <v>13</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_3.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_3.xlsx
@@ -460,13 +460,13 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>108.52</v>
+        <v>108.59</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
       <c r="F2">
-        <v>105.72</v>
+        <v>113.79</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -480,13 +480,13 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>92.62</v>
+        <v>93.89</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
       </c>
       <c r="F3">
-        <v>94.47</v>
+        <v>117.54</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -500,13 +500,13 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>136.52</v>
+        <v>136.59</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
       </c>
       <c r="F4">
-        <v>111.22</v>
+        <v>111.29</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -520,13 +520,13 @@
         <v>13</v>
       </c>
       <c r="D5">
-        <v>87.92</v>
+        <v>97.79000000000001</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
       </c>
       <c r="F5">
-        <v>97.62</v>
+        <v>106.39</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_3.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_3.xlsx
@@ -460,13 +460,13 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>108.59</v>
+        <v>108.58984375</v>
       </c>
       <c r="E2" t="s">
         <v>14</v>
       </c>
       <c r="F2">
-        <v>113.79</v>
+        <v>113.7900390625</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -480,13 +480,13 @@
         <v>11</v>
       </c>
       <c r="D3">
-        <v>93.89</v>
+        <v>93.89013671875</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
       </c>
       <c r="F3">
-        <v>117.54</v>
+        <v>117.5400390625</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -500,13 +500,13 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>136.59</v>
+        <v>136.58984375</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
       </c>
       <c r="F4">
-        <v>111.29</v>
+        <v>111.2900390625</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -520,13 +520,13 @@
         <v>13</v>
       </c>
       <c r="D5">
-        <v>97.79000000000001</v>
+        <v>97.7900390625</v>
       </c>
       <c r="E5" t="s">
         <v>17</v>
       </c>
       <c r="F5">
-        <v>106.39</v>
+        <v>106.39013671875</v>
       </c>
     </row>
   </sheetData>

--- a/libertadores/datasets_liberta/resultados_fase_3.xlsx
+++ b/libertadores/datasets_liberta/resultados_fase_3.xlsx
@@ -569,8 +569,14 @@
       <c r="C2" t="s">
         <v>14</v>
       </c>
+      <c r="D2">
+        <v>76.9501953125</v>
+      </c>
       <c r="E2" t="s">
         <v>10</v>
+      </c>
+      <c r="F2">
+        <v>49.280029296875</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -583,8 +589,14 @@
       <c r="C3" t="s">
         <v>15</v>
       </c>
+      <c r="D3">
+        <v>53.139892578125</v>
+      </c>
       <c r="E3" t="s">
         <v>11</v>
+      </c>
+      <c r="F3">
+        <v>48.580078125</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -597,8 +609,14 @@
       <c r="C4" t="s">
         <v>16</v>
       </c>
+      <c r="D4">
+        <v>47.050048828125</v>
+      </c>
       <c r="E4" t="s">
         <v>12</v>
+      </c>
+      <c r="F4">
+        <v>46.050048828125</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -611,8 +629,14 @@
       <c r="C5" t="s">
         <v>17</v>
       </c>
+      <c r="D5">
+        <v>51.8798828125</v>
+      </c>
       <c r="E5" t="s">
         <v>13</v>
+      </c>
+      <c r="F5">
+        <v>62.050048828125</v>
       </c>
     </row>
   </sheetData>
